--- a/src/Assets/Tables.xlsx
+++ b/src/Assets/Tables.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Harsh\company\github\harsh-maheshwari.github.io\src\Assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26284B23-987C-4A00-B316-36A8423C808C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E72F868-C145-4A31-93B6-4B0AE9AA1A99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="1" xr2:uid="{34CD1E43-5044-FC47-9ADD-5FB11EB3BB61}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="2" xr2:uid="{34CD1E43-5044-FC47-9ADD-5FB11EB3BB61}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="153">
   <si>
     <t>False positive (FP), type I error, false alarm, overestimation</t>
   </si>
@@ -436,6 +437,63 @@
   </si>
   <si>
     <t>Contact Me</t>
+  </si>
+  <si>
+    <t>Data preprocessing option</t>
+  </si>
+  <si>
+    <t>Instance-level (stateless transformations)</t>
+  </si>
+  <si>
+    <t>Full-pass during training and instance-level during serving    (stateful transformations)</t>
+  </si>
+  <si>
+    <t>Real-time (window) aggregations during training and serving (streaming    transformations)</t>
+  </si>
+  <si>
+    <t>BigQuery (SQL)</t>
+  </si>
+  <si>
+    <t>Batch scoring: OK —the same transformation implementation is      applied on data during training and batch scoring. Online prediction: Not recommended —you can process training data,      but it results in training-serving skew because you process serving data      using different tools.</t>
+  </si>
+  <si>
+    <t>Batch scoring: Not recommended . Online prediction: Not recommended . Although you can use statistics computed using BigQuery      for instance-level batch/online transformations, it isn't easy because      you must maintain a stats store to be populated during training and      used during prediction.</t>
+  </si>
+  <si>
+    <t>Batch scoring: N/A —aggregates like these are computed based on      real-time events. Online prediction: Not recommended —you can process training data,      but it results in training-serving skew because you process serving data      using different tools.</t>
+  </si>
+  <si>
+    <t>Dataflow (Apache Beam)</t>
+  </si>
+  <si>
+    <t>Batch scoring: OK —the same transformation implementation is      applied on data during training and batch scoring. Online prediction: OK —if data at serving time comes from      Pub/Sub to be consumed by Dataflow.      Otherwise, results in training-serving skew.</t>
+  </si>
+  <si>
+    <t>Batch scoring: Not recommended . Online predictions: Not recommended . Although you can use statistics computed using Dataflow      for instance-level batch/online transformations, it isn't easy      because you must maintain a stats store to be populated during training      and used during prediction.</t>
+  </si>
+  <si>
+    <t>Batch scoring: N/A —aggregates like these are computed      based on real-time events. Online prediction: OK —the same Apache Beam transformation is      applied on data during training (batch) and serving (stream).</t>
+  </si>
+  <si>
+    <t>Dataflow (Apache Beam + TFT)</t>
+  </si>
+  <si>
+    <t>Batch scoring: OK —the same transformation implementation is      applied to data during training and batch scoring. Online prediction: Recommended —it avoids training-serving skew      and prepares training data up front.</t>
+  </si>
+  <si>
+    <t>Batch scoring: Recommended . Online prediction: Recommended . Both uses are recommended because transformation logic and computed      statistics during training are stored as a TensorFlow      graph that's attached to the exported model for serving.</t>
+  </si>
+  <si>
+    <t>TensorFlow * ( input_fn &amp; serving_fn )</t>
+  </si>
+  <si>
+    <t>Batch scoring: Not recommended . Online prediction: Not recommended . For training efficiency in both cases, it's better to prepare the      training data up front.</t>
+  </si>
+  <si>
+    <t>Batch scoring: Not Possible . Online prediction: Not Possible .</t>
+  </si>
+  <si>
+    <t>Batch scoring: N/A —aggregates like these are computed      based on real-time events. Online prediction: Not Possible .</t>
   </si>
 </sst>
 </file>
@@ -1393,4 +1451,84 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8EF27665-5FC8-4689-81CD-68EFAA7D5B26}">
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B1" t="s">
+        <v>135</v>
+      </c>
+      <c r="C1" t="s">
+        <v>136</v>
+      </c>
+      <c r="D1" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>138</v>
+      </c>
+      <c r="B2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C2" t="s">
+        <v>140</v>
+      </c>
+      <c r="D2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>142</v>
+      </c>
+      <c r="B3" t="s">
+        <v>143</v>
+      </c>
+      <c r="C3" t="s">
+        <v>144</v>
+      </c>
+      <c r="D3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>146</v>
+      </c>
+      <c r="B4" t="s">
+        <v>147</v>
+      </c>
+      <c r="C4" t="s">
+        <v>148</v>
+      </c>
+      <c r="D4" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B5" t="s">
+        <v>150</v>
+      </c>
+      <c r="C5" t="s">
+        <v>151</v>
+      </c>
+      <c r="D5" t="s">
+        <v>152</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/src/Assets/Tables.xlsx
+++ b/src/Assets/Tables.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25831"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11211"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Harsh\company\github\harsh-maheshwari.github.io\src\Assets\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/ELEMEMTS_H/company/github/harsh-maheshwari.github.io/src/Assets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E72F868-C145-4A31-93B6-4B0AE9AA1A99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{119969AD-D3CD-2D4C-BF2C-33A97DA2F978}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="2" xr2:uid="{34CD1E43-5044-FC47-9ADD-5FB11EB3BB61}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="35840" windowHeight="22400" xr2:uid="{34CD1E43-5044-FC47-9ADD-5FB11EB3BB61}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="161">
   <si>
     <t>False positive (FP), type I error, false alarm, overestimation</t>
   </si>
@@ -494,6 +494,30 @@
   </si>
   <si>
     <t>Batch scoring: N/A —aggregates like these are computed      based on real-time events. Online prediction: Not Possible .</t>
+  </si>
+  <si>
+    <t>[Data Analytics Services for MSMEs](Services/2022-12-29 Services#data-analytics-services-for-msmes)</t>
+  </si>
+  <si>
+    <t>[Predictive Data Modeling and Forecasting](Services/2022-12-29 Services#predictive-data-modeling-and-forecasting)</t>
+  </si>
+  <si>
+    <t>[Data Science Consulting Services](Services/2022-12-29 Services#data-science-consulting-services)</t>
+  </si>
+  <si>
+    <t>[Data Integration Software Development](Services/2022-12-29 Services#data-integration-software-development)</t>
+  </si>
+  <si>
+    <t>[Data Science Recruitment](Services/2022-12-29 Services#data-science-recruitment)</t>
+  </si>
+  <si>
+    <t>[Data Science Education and Training](Services/2022-12-29 Services#data-science-education-and-training)</t>
+  </si>
+  <si>
+    <t>[Product and Market Development](Services/2022-12-29 Services#product-and-market-development)</t>
+  </si>
+  <si>
+    <t>Services</t>
   </si>
 </sst>
 </file>
@@ -569,7 +593,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2013 - 2022">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -857,7 +881,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme 2013 - 2022" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -865,19 +889,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{095F115B-440C-0845-90BD-CDCAD3191863}">
-  <dimension ref="A1:E43"/>
-  <sheetFormatPr defaultColWidth="10.796875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:E55"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="44.19921875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="50.19921875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="48.19921875" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="55.69921875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="69.69921875" style="1" customWidth="1"/>
-    <col min="6" max="8" width="20.796875" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="10.796875" style="1"/>
+    <col min="1" max="1" width="44.1640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="50.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="48.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="55.6640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="69.6640625" style="1" customWidth="1"/>
+    <col min="6" max="8" width="20.83203125" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>9</v>
       </c>
@@ -886,7 +910,7 @@
       <c r="D1" s="4"/>
       <c r="E1" s="4"/>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" ht="17" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>13</v>
       </c>
@@ -900,7 +924,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" ht="17" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>14</v>
       </c>
@@ -911,7 +935,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" ht="34" hidden="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
@@ -922,7 +946,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" ht="34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>16</v>
       </c>
@@ -933,7 +957,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" ht="17" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>17</v>
       </c>
@@ -944,7 +968,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" ht="17" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>18</v>
       </c>
@@ -955,7 +979,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
         <v>22</v>
       </c>
@@ -969,12 +993,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
         <v>20</v>
       </c>
@@ -985,7 +1009,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:3" ht="34" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
         <v>21</v>
       </c>
@@ -996,7 +1020,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3" ht="34" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
         <v>24</v>
       </c>
@@ -1007,12 +1031,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
         <v>26</v>
       </c>
@@ -1023,12 +1047,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
         <v>28</v>
       </c>
@@ -1039,9 +1063,43 @@
         <v>7</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
         <v>29</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" ht="17" x14ac:dyDescent="0.2">
+      <c r="A51" s="1" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" ht="34" x14ac:dyDescent="0.2">
+      <c r="A52" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" ht="34" x14ac:dyDescent="0.2">
+      <c r="A53" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" ht="34" x14ac:dyDescent="0.2">
+      <c r="A54" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" ht="34" x14ac:dyDescent="0.2">
+      <c r="A55" s="1" t="s">
+        <v>159</v>
       </c>
     </row>
   </sheetData>
@@ -1055,17 +1113,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F5D18C4-CBEA-4C63-81A9-69015E02E977}">
   <dimension ref="A1:E38"/>
-  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="46.796875" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="35.19921875" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32.09765625" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="41.69921875" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="46.83203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="35.1640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.1640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="41.6640625" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="20.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="8.796875" style="2"/>
+    <col min="6" max="16384" width="8.83203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>30</v>
       </c>
@@ -1079,7 +1137,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>33</v>
       </c>
@@ -1093,7 +1151,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>128</v>
       </c>
@@ -1107,7 +1165,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>34</v>
       </c>
@@ -1121,7 +1179,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>37</v>
       </c>
@@ -1135,7 +1193,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>40</v>
       </c>
@@ -1149,7 +1207,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>44</v>
       </c>
@@ -1163,7 +1221,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
         <v>47</v>
       </c>
@@ -1180,7 +1238,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>52</v>
       </c>
@@ -1197,7 +1255,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>56</v>
       </c>
@@ -1214,7 +1272,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>60</v>
       </c>
@@ -1231,7 +1289,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>64</v>
       </c>
@@ -1248,7 +1306,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
         <v>68</v>
       </c>
@@ -1262,7 +1320,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
         <v>72</v>
       </c>
@@ -1276,7 +1334,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
         <v>76</v>
       </c>
@@ -1290,7 +1348,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
         <v>80</v>
       </c>
@@ -1304,7 +1362,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
         <v>84</v>
       </c>
@@ -1318,7 +1376,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
         <v>88</v>
       </c>
@@ -1332,7 +1390,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
         <v>92</v>
       </c>
@@ -1346,7 +1404,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
         <v>96</v>
       </c>
@@ -1360,7 +1418,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
         <v>100</v>
       </c>
@@ -1374,7 +1432,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
         <v>104</v>
       </c>
@@ -1388,7 +1446,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
         <v>108</v>
       </c>
@@ -1402,7 +1460,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
         <v>112</v>
       </c>
@@ -1410,7 +1468,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
         <v>114</v>
       </c>
@@ -1418,22 +1476,22 @@
         <v>115</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B35" s="2" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B36" s="2" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
         <v>129</v>
       </c>
@@ -1456,9 +1514,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8EF27665-5FC8-4689-81CD-68EFAA7D5B26}">
   <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>134</v>
       </c>
@@ -1472,7 +1530,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>138</v>
       </c>
@@ -1486,7 +1544,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>142</v>
       </c>
@@ -1500,7 +1558,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>146</v>
       </c>
@@ -1514,7 +1572,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>149</v>
       </c>

--- a/src/Assets/Tables.xlsx
+++ b/src/Assets/Tables.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/ELEMEMTS_H/company/github/harsh-maheshwari.github.io/src/Assets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{119969AD-D3CD-2D4C-BF2C-33A97DA2F978}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{151B67D5-AC37-C74E-94B3-568551698C34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="35840" windowHeight="22400" xr2:uid="{34CD1E43-5044-FC47-9ADD-5FB11EB3BB61}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="35840" windowHeight="20200" xr2:uid="{34CD1E43-5044-FC47-9ADD-5FB11EB3BB61}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="247">
   <si>
     <t>False positive (FP), type I error, false alarm, overestimation</t>
   </si>
@@ -496,35 +496,293 @@
     <t>Batch scoring: N/A —aggregates like these are computed      based on real-time events. Online prediction: Not Possible .</t>
   </si>
   <si>
-    <t>[Data Analytics Services for MSMEs](Services/2022-12-29 Services#data-analytics-services-for-msmes)</t>
-  </si>
-  <si>
-    <t>[Predictive Data Modeling and Forecasting](Services/2022-12-29 Services#predictive-data-modeling-and-forecasting)</t>
-  </si>
-  <si>
-    <t>[Data Science Consulting Services](Services/2022-12-29 Services#data-science-consulting-services)</t>
-  </si>
-  <si>
-    <t>[Data Integration Software Development](Services/2022-12-29 Services#data-integration-software-development)</t>
-  </si>
-  <si>
-    <t>[Data Science Recruitment](Services/2022-12-29 Services#data-science-recruitment)</t>
-  </si>
-  <si>
-    <t>[Data Science Education and Training](Services/2022-12-29 Services#data-science-education-and-training)</t>
-  </si>
-  <si>
-    <t>[Product and Market Development](Services/2022-12-29 Services#product-and-market-development)</t>
-  </si>
-  <si>
-    <t>Services</t>
+    <t>Concept</t>
+  </si>
+  <si>
+    <t>Label</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Risk factor calculation</t>
+  </si>
+  <si>
+    <t>Size: Market equity (ME)</t>
+  </si>
+  <si>
+    <t>SMB</t>
+  </si>
+  <si>
+    <t>Small minus big</t>
+  </si>
+  <si>
+    <t>Nine small stock PF minus nine large stock PF.</t>
+  </si>
+  <si>
+    <t>Value: Book value of equity (BE) divided by ME</t>
+  </si>
+  <si>
+    <t>HML</t>
+  </si>
+  <si>
+    <t>High minus low</t>
+  </si>
+  <si>
+    <t>Two value PF minus two growth (with low BE/ME value) PF.</t>
+  </si>
+  <si>
+    <t>Operating profitability (OP): Revenue minus cost of goods sold/assets</t>
+  </si>
+  <si>
+    <t>RMW</t>
+  </si>
+  <si>
+    <t>Robust minus weak</t>
+  </si>
+  <si>
+    <t>Two robust OP PF minus two weak OP PF.</t>
+  </si>
+  <si>
+    <t>Investment: Investment/assets</t>
+  </si>
+  <si>
+    <t>CMA</t>
+  </si>
+  <si>
+    <t>Conservative minus aggressive</t>
+  </si>
+  <si>
+    <t>Two conservative investment portfolios, minus two aggressive investment portfolios.</t>
+  </si>
+  <si>
+    <t>Market</t>
+  </si>
+  <si>
+    <t>Rm-Rf</t>
+  </si>
+  <si>
+    <t>Excess return on the market</t>
+  </si>
+  <si>
+    <t>Value-weight return of all firms incorporated in and listed on major US exchanges with good data, minus the one-month Treasury bill rate.</t>
+  </si>
+  <si>
+    <t>Instrument</t>
+  </si>
+  <si>
+    <t>Buy Order [BO]</t>
+  </si>
+  <si>
+    <t>Sell Order [SO]</t>
+  </si>
+  <si>
+    <t>Calculation</t>
+  </si>
+  <si>
+    <t>Gold</t>
+  </si>
+  <si>
+    <t>Entry</t>
+  </si>
+  <si>
+    <t>Target</t>
+  </si>
+  <si>
+    <t>FSL</t>
+  </si>
+  <si>
+    <t>MSL</t>
+  </si>
+  <si>
+    <t>TSL</t>
+  </si>
+  <si>
+    <t>Buy / Long</t>
+  </si>
+  <si>
+    <t>3DHH + 0.12%</t>
+  </si>
+  <si>
+    <t>Buy Entry + 1.2%</t>
+  </si>
+  <si>
+    <t>Max (MSL,TSL)</t>
+  </si>
+  <si>
+    <t>Buy Entry -1.2%</t>
+  </si>
+  <si>
+    <t>2DLL - 0.12%</t>
+  </si>
+  <si>
+    <t>Sell / Short</t>
+  </si>
+  <si>
+    <t>3DLL - 0.12%</t>
+  </si>
+  <si>
+    <t>Sell Entry - 1.2%</t>
+  </si>
+  <si>
+    <t>Min (MSL,TSL)</t>
+  </si>
+  <si>
+    <t>Sell Entry +1.2%</t>
+  </si>
+  <si>
+    <t>2DHH + 0.12%</t>
+  </si>
+  <si>
+    <t>Silver</t>
+  </si>
+  <si>
+    <t>2DHH + 0.2%</t>
+  </si>
+  <si>
+    <t>Buy Entry + 2%</t>
+  </si>
+  <si>
+    <t>Buy Entry - 2%</t>
+  </si>
+  <si>
+    <t>2DLL - 0.2%</t>
+  </si>
+  <si>
+    <t>Sell Entry - 2%</t>
+  </si>
+  <si>
+    <t>Sell Entry + 2%</t>
+  </si>
+  <si>
+    <t>Crude</t>
+  </si>
+  <si>
+    <t>2DHH + 0.4%</t>
+  </si>
+  <si>
+    <t>Buy Entry + 4%</t>
+  </si>
+  <si>
+    <t>Buy Entry - 4%</t>
+  </si>
+  <si>
+    <t>2DLL - 0.4%</t>
+  </si>
+  <si>
+    <t>Sell Entry - 4%</t>
+  </si>
+  <si>
+    <t>Sell Entry + 4%</t>
+  </si>
+  <si>
+    <t>Bank Nifty Futures</t>
+  </si>
+  <si>
+    <t>2DHH + 0.15%</t>
+  </si>
+  <si>
+    <t>Buy Entry + 1.5%</t>
+  </si>
+  <si>
+    <t>Buy Entry - 1.5%</t>
+  </si>
+  <si>
+    <t>2DLL - 0.15%</t>
+  </si>
+  <si>
+    <t>Sell Entry - 1.5%</t>
+  </si>
+  <si>
+    <t>Sell Entry + 1.5%</t>
+  </si>
+  <si>
+    <t>Nifty Futures</t>
+  </si>
+  <si>
+    <t>Buy Entry - 1.2%</t>
+  </si>
+  <si>
+    <t>Sell Entry + 1.2%</t>
+  </si>
+  <si>
+    <t>Stock Futures</t>
+  </si>
+  <si>
+    <t>BO / SO</t>
+  </si>
+  <si>
+    <t>Lots</t>
+  </si>
+  <si>
+    <t>Trigger Price / Price</t>
+  </si>
+  <si>
+    <t>Nil</t>
+  </si>
+  <si>
+    <t>Buy and Target not achieved</t>
+  </si>
+  <si>
+    <t>Buy and Target achieved</t>
+  </si>
+  <si>
+    <t>Sell and Target not achieved</t>
+  </si>
+  <si>
+    <t>Sell and Target achieved</t>
+  </si>
+  <si>
+    <t>Buy Entry</t>
+  </si>
+  <si>
+    <t>BO</t>
+  </si>
+  <si>
+    <t>Trigger Price</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>Buy Target</t>
+  </si>
+  <si>
+    <t>SO</t>
+  </si>
+  <si>
+    <t>Price</t>
+  </si>
+  <si>
+    <t>Buy Stop Loss 1</t>
+  </si>
+  <si>
+    <t>Buy Stop Loss 2</t>
+  </si>
+  <si>
+    <t>Sell Entry</t>
+  </si>
+  <si>
+    <t>Sell Target</t>
+  </si>
+  <si>
+    <t>Sell Stop Loss 1</t>
+  </si>
+  <si>
+    <t>Sell Stop Loss 2</t>
+  </si>
+  <si>
+    <t>Position Entries</t>
+  </si>
+  <si>
+    <t>Trade Step</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -540,16 +798,77 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Montserrat"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Montserrat"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Montserrat"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Montserrat"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA4C2F4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB6D7A8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA9999"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFE599"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -557,11 +876,63 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -572,7 +943,70 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -889,7 +1323,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{095F115B-440C-0845-90BD-CDCAD3191863}">
-  <dimension ref="A1:E55"/>
+  <dimension ref="A1:I117"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="44.1640625" style="1" customWidth="1"/>
@@ -902,13 +1336,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
     </row>
     <row r="2" spans="1:5" ht="17" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
@@ -1068,38 +1502,926 @@
         <v>29</v>
       </c>
     </row>
-    <row r="51" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A51" s="1" t="s">
+    <row r="58" spans="1:4" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="59" spans="1:4" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="C59" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D59" s="5" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="B60" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="C60" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="D60" s="7" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="52" spans="1:2" ht="34" x14ac:dyDescent="0.2">
-      <c r="A52" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" ht="34" x14ac:dyDescent="0.2">
-      <c r="A53" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" ht="34" x14ac:dyDescent="0.2">
-      <c r="A54" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" ht="34" x14ac:dyDescent="0.2">
-      <c r="A55" s="1" t="s">
-        <v>159</v>
+    <row r="61" spans="1:4" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="B61" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="C61" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="D61" s="7" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" ht="33" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="B62" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="C62" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="D62" s="7" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" ht="33" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="B63" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="C63" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="D63" s="7" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" ht="33" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="B64" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="C64" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="D64" s="7" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="74" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="B74" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="C74" s="11" t="s">
+        <v>179</v>
+      </c>
+      <c r="D74" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="E74" s="13"/>
+      <c r="F74" s="13"/>
+    </row>
+    <row r="75" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="14" t="s">
+        <v>181</v>
+      </c>
+      <c r="B75" s="15" t="s">
+        <v>182</v>
+      </c>
+      <c r="C75" s="15" t="s">
+        <v>183</v>
+      </c>
+      <c r="D75" s="15" t="s">
+        <v>184</v>
+      </c>
+      <c r="E75" s="15" t="s">
+        <v>185</v>
+      </c>
+      <c r="F75" s="15" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="B76" s="17" t="s">
+        <v>188</v>
+      </c>
+      <c r="C76" s="18" t="s">
+        <v>189</v>
+      </c>
+      <c r="D76" s="18" t="s">
+        <v>190</v>
+      </c>
+      <c r="E76" s="19" t="s">
+        <v>191</v>
+      </c>
+      <c r="F76" s="19" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="16" t="s">
+        <v>193</v>
+      </c>
+      <c r="B77" s="18" t="s">
+        <v>194</v>
+      </c>
+      <c r="C77" s="17" t="s">
+        <v>195</v>
+      </c>
+      <c r="D77" s="17" t="s">
+        <v>196</v>
+      </c>
+      <c r="E77" s="19" t="s">
+        <v>197</v>
+      </c>
+      <c r="F77" s="19" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="14" t="s">
+        <v>199</v>
+      </c>
+      <c r="B78" s="15" t="s">
+        <v>182</v>
+      </c>
+      <c r="C78" s="15" t="s">
+        <v>183</v>
+      </c>
+      <c r="D78" s="15" t="s">
+        <v>184</v>
+      </c>
+      <c r="E78" s="15" t="s">
+        <v>185</v>
+      </c>
+      <c r="F78" s="15" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="B79" s="17" t="s">
+        <v>200</v>
+      </c>
+      <c r="C79" s="18" t="s">
+        <v>201</v>
+      </c>
+      <c r="D79" s="18" t="s">
+        <v>190</v>
+      </c>
+      <c r="E79" s="19" t="s">
+        <v>202</v>
+      </c>
+      <c r="F79" s="19" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="16" t="s">
+        <v>193</v>
+      </c>
+      <c r="B80" s="18" t="s">
+        <v>203</v>
+      </c>
+      <c r="C80" s="17" t="s">
+        <v>204</v>
+      </c>
+      <c r="D80" s="17" t="s">
+        <v>196</v>
+      </c>
+      <c r="E80" s="19" t="s">
+        <v>205</v>
+      </c>
+      <c r="F80" s="19" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="14" t="s">
+        <v>206</v>
+      </c>
+      <c r="B81" s="15" t="s">
+        <v>182</v>
+      </c>
+      <c r="C81" s="15" t="s">
+        <v>183</v>
+      </c>
+      <c r="D81" s="15" t="s">
+        <v>184</v>
+      </c>
+      <c r="E81" s="15" t="s">
+        <v>185</v>
+      </c>
+      <c r="F81" s="15" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="B82" s="17" t="s">
+        <v>207</v>
+      </c>
+      <c r="C82" s="18" t="s">
+        <v>208</v>
+      </c>
+      <c r="D82" s="18" t="s">
+        <v>190</v>
+      </c>
+      <c r="E82" s="19" t="s">
+        <v>209</v>
+      </c>
+      <c r="F82" s="19" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A83" s="16" t="s">
+        <v>193</v>
+      </c>
+      <c r="B83" s="18" t="s">
+        <v>210</v>
+      </c>
+      <c r="C83" s="17" t="s">
+        <v>211</v>
+      </c>
+      <c r="D83" s="17" t="s">
+        <v>196</v>
+      </c>
+      <c r="E83" s="19" t="s">
+        <v>212</v>
+      </c>
+      <c r="F83" s="19" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="14" t="s">
+        <v>213</v>
+      </c>
+      <c r="B84" s="15" t="s">
+        <v>182</v>
+      </c>
+      <c r="C84" s="15" t="s">
+        <v>183</v>
+      </c>
+      <c r="D84" s="15" t="s">
+        <v>184</v>
+      </c>
+      <c r="E84" s="15" t="s">
+        <v>185</v>
+      </c>
+      <c r="F84" s="15" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A85" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="B85" s="17" t="s">
+        <v>214</v>
+      </c>
+      <c r="C85" s="18" t="s">
+        <v>215</v>
+      </c>
+      <c r="D85" s="18" t="s">
+        <v>190</v>
+      </c>
+      <c r="E85" s="19" t="s">
+        <v>216</v>
+      </c>
+      <c r="F85" s="19" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="16" t="s">
+        <v>193</v>
+      </c>
+      <c r="B86" s="18" t="s">
+        <v>217</v>
+      </c>
+      <c r="C86" s="17" t="s">
+        <v>218</v>
+      </c>
+      <c r="D86" s="17" t="s">
+        <v>196</v>
+      </c>
+      <c r="E86" s="19" t="s">
+        <v>219</v>
+      </c>
+      <c r="F86" s="19" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="14" t="s">
+        <v>220</v>
+      </c>
+      <c r="B87" s="15" t="s">
+        <v>182</v>
+      </c>
+      <c r="C87" s="15" t="s">
+        <v>183</v>
+      </c>
+      <c r="D87" s="15" t="s">
+        <v>184</v>
+      </c>
+      <c r="E87" s="15" t="s">
+        <v>185</v>
+      </c>
+      <c r="F87" s="15" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="B88" s="17" t="s">
+        <v>198</v>
+      </c>
+      <c r="C88" s="18" t="s">
+        <v>189</v>
+      </c>
+      <c r="D88" s="18" t="s">
+        <v>190</v>
+      </c>
+      <c r="E88" s="19" t="s">
+        <v>221</v>
+      </c>
+      <c r="F88" s="19" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A89" s="16" t="s">
+        <v>193</v>
+      </c>
+      <c r="B89" s="18" t="s">
+        <v>192</v>
+      </c>
+      <c r="C89" s="17" t="s">
+        <v>195</v>
+      </c>
+      <c r="D89" s="17" t="s">
+        <v>196</v>
+      </c>
+      <c r="E89" s="19" t="s">
+        <v>222</v>
+      </c>
+      <c r="F89" s="19" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A90" s="14" t="s">
+        <v>223</v>
+      </c>
+      <c r="B90" s="15" t="s">
+        <v>182</v>
+      </c>
+      <c r="C90" s="15" t="s">
+        <v>183</v>
+      </c>
+      <c r="D90" s="15" t="s">
+        <v>184</v>
+      </c>
+      <c r="E90" s="15" t="s">
+        <v>185</v>
+      </c>
+      <c r="F90" s="15" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A91" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="B91" s="20"/>
+      <c r="C91" s="21"/>
+      <c r="D91" s="21"/>
+      <c r="E91" s="22"/>
+      <c r="F91" s="22"/>
+    </row>
+    <row r="92" spans="1:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A92" s="16" t="s">
+        <v>193</v>
+      </c>
+      <c r="B92" s="21"/>
+      <c r="C92" s="20"/>
+      <c r="D92" s="20"/>
+      <c r="E92" s="22"/>
+      <c r="F92" s="22"/>
+    </row>
+    <row r="94" spans="1:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="95" spans="1:9" ht="37" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A95" s="24" t="s">
+        <v>245</v>
+      </c>
+      <c r="B95" s="23" t="s">
+        <v>224</v>
+      </c>
+      <c r="C95" s="23" t="s">
+        <v>225</v>
+      </c>
+      <c r="D95" s="23" t="s">
+        <v>226</v>
+      </c>
+      <c r="E95" s="23" t="s">
+        <v>227</v>
+      </c>
+      <c r="F95" s="23" t="s">
+        <v>228</v>
+      </c>
+      <c r="G95" s="23" t="s">
+        <v>229</v>
+      </c>
+      <c r="H95" s="23" t="s">
+        <v>230</v>
+      </c>
+      <c r="I95" s="23" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A96" s="24" t="s">
+        <v>232</v>
+      </c>
+      <c r="B96" s="25" t="s">
+        <v>233</v>
+      </c>
+      <c r="C96" s="25">
+        <v>2</v>
+      </c>
+      <c r="D96" s="25" t="s">
+        <v>234</v>
+      </c>
+      <c r="E96" s="25" t="s">
+        <v>235</v>
+      </c>
+      <c r="F96" s="25"/>
+      <c r="G96" s="25"/>
+      <c r="H96" s="25" t="s">
+        <v>235</v>
+      </c>
+      <c r="I96" s="25" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A97" s="24" t="s">
+        <v>236</v>
+      </c>
+      <c r="B97" s="25" t="s">
+        <v>237</v>
+      </c>
+      <c r="C97" s="25">
+        <v>1</v>
+      </c>
+      <c r="D97" s="25" t="s">
+        <v>238</v>
+      </c>
+      <c r="E97" s="25" t="s">
+        <v>235</v>
+      </c>
+      <c r="F97" s="25" t="s">
+        <v>235</v>
+      </c>
+      <c r="G97" s="25"/>
+      <c r="H97" s="25" t="s">
+        <v>235</v>
+      </c>
+      <c r="I97" s="25" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A98" s="24" t="s">
+        <v>239</v>
+      </c>
+      <c r="B98" s="25" t="s">
+        <v>237</v>
+      </c>
+      <c r="C98" s="25">
+        <v>2</v>
+      </c>
+      <c r="D98" s="25" t="s">
+        <v>234</v>
+      </c>
+      <c r="E98" s="25"/>
+      <c r="F98" s="25" t="s">
+        <v>235</v>
+      </c>
+      <c r="G98" s="25"/>
+      <c r="H98" s="25"/>
+      <c r="I98" s="25"/>
+    </row>
+    <row r="99" spans="1:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A99" s="24" t="s">
+        <v>240</v>
+      </c>
+      <c r="B99" s="25" t="s">
+        <v>237</v>
+      </c>
+      <c r="C99" s="25">
+        <v>1</v>
+      </c>
+      <c r="D99" s="25" t="s">
+        <v>234</v>
+      </c>
+      <c r="E99" s="25"/>
+      <c r="F99" s="25"/>
+      <c r="G99" s="25" t="s">
+        <v>235</v>
+      </c>
+      <c r="H99" s="25"/>
+      <c r="I99" s="25"/>
+    </row>
+    <row r="100" spans="1:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A100" s="24" t="s">
+        <v>241</v>
+      </c>
+      <c r="B100" s="25" t="s">
+        <v>237</v>
+      </c>
+      <c r="C100" s="25">
+        <v>2</v>
+      </c>
+      <c r="D100" s="25" t="s">
+        <v>234</v>
+      </c>
+      <c r="E100" s="25" t="s">
+        <v>235</v>
+      </c>
+      <c r="F100" s="25" t="s">
+        <v>235</v>
+      </c>
+      <c r="G100" s="25" t="s">
+        <v>235</v>
+      </c>
+      <c r="H100" s="25"/>
+      <c r="I100" s="25"/>
+    </row>
+    <row r="101" spans="1:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A101" s="24" t="s">
+        <v>242</v>
+      </c>
+      <c r="B101" s="25" t="s">
+        <v>233</v>
+      </c>
+      <c r="C101" s="25">
+        <v>1</v>
+      </c>
+      <c r="D101" s="25" t="s">
+        <v>238</v>
+      </c>
+      <c r="E101" s="25" t="s">
+        <v>235</v>
+      </c>
+      <c r="F101" s="25" t="s">
+        <v>235</v>
+      </c>
+      <c r="G101" s="25" t="s">
+        <v>235</v>
+      </c>
+      <c r="H101" s="25" t="s">
+        <v>235</v>
+      </c>
+      <c r="I101" s="25"/>
+    </row>
+    <row r="102" spans="1:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A102" s="24" t="s">
+        <v>243</v>
+      </c>
+      <c r="B102" s="25" t="s">
+        <v>233</v>
+      </c>
+      <c r="C102" s="25">
+        <v>2</v>
+      </c>
+      <c r="D102" s="25" t="s">
+        <v>234</v>
+      </c>
+      <c r="E102" s="25"/>
+      <c r="F102" s="25"/>
+      <c r="G102" s="25"/>
+      <c r="H102" s="25" t="s">
+        <v>235</v>
+      </c>
+      <c r="I102" s="25"/>
+    </row>
+    <row r="103" spans="1:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A103" s="24" t="s">
+        <v>244</v>
+      </c>
+      <c r="B103" s="25" t="s">
+        <v>233</v>
+      </c>
+      <c r="C103" s="25">
+        <v>1</v>
+      </c>
+      <c r="D103" s="25" t="s">
+        <v>234</v>
+      </c>
+      <c r="E103" s="25"/>
+      <c r="F103" s="25"/>
+      <c r="G103" s="25"/>
+      <c r="H103" s="25"/>
+      <c r="I103" s="25" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="106" spans="1:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B106" s="9"/>
+      <c r="C106" s="10"/>
+      <c r="D106" s="11"/>
+      <c r="E106" s="12"/>
+      <c r="F106" s="13"/>
+      <c r="G106" s="13"/>
+    </row>
+    <row r="107" spans="1:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A107" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="B107" s="14" t="s">
+        <v>246</v>
+      </c>
+      <c r="C107" s="15" t="s">
+        <v>182</v>
+      </c>
+      <c r="D107" s="15" t="s">
+        <v>183</v>
+      </c>
+      <c r="E107" s="15" t="s">
+        <v>184</v>
+      </c>
+      <c r="F107" s="15" t="s">
+        <v>185</v>
+      </c>
+      <c r="G107" s="15" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A108" s="14" t="s">
+        <v>181</v>
+      </c>
+      <c r="B108" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="C108" s="17" t="s">
+        <v>188</v>
+      </c>
+      <c r="D108" s="18" t="s">
+        <v>189</v>
+      </c>
+      <c r="E108" s="18" t="s">
+        <v>190</v>
+      </c>
+      <c r="F108" s="19" t="s">
+        <v>191</v>
+      </c>
+      <c r="G108" s="19" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A109" s="14" t="s">
+        <v>181</v>
+      </c>
+      <c r="B109" s="16" t="s">
+        <v>193</v>
+      </c>
+      <c r="C109" s="18" t="s">
+        <v>194</v>
+      </c>
+      <c r="D109" s="17" t="s">
+        <v>195</v>
+      </c>
+      <c r="E109" s="17" t="s">
+        <v>196</v>
+      </c>
+      <c r="F109" s="19" t="s">
+        <v>197</v>
+      </c>
+      <c r="G109" s="19" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A110" s="14" t="s">
+        <v>199</v>
+      </c>
+      <c r="B110" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="C110" s="17" t="s">
+        <v>200</v>
+      </c>
+      <c r="D110" s="18" t="s">
+        <v>201</v>
+      </c>
+      <c r="E110" s="18" t="s">
+        <v>190</v>
+      </c>
+      <c r="F110" s="19" t="s">
+        <v>202</v>
+      </c>
+      <c r="G110" s="19" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A111" s="14" t="s">
+        <v>199</v>
+      </c>
+      <c r="B111" s="16" t="s">
+        <v>193</v>
+      </c>
+      <c r="C111" s="18" t="s">
+        <v>203</v>
+      </c>
+      <c r="D111" s="17" t="s">
+        <v>204</v>
+      </c>
+      <c r="E111" s="17" t="s">
+        <v>196</v>
+      </c>
+      <c r="F111" s="19" t="s">
+        <v>205</v>
+      </c>
+      <c r="G111" s="19" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A112" s="14" t="s">
+        <v>206</v>
+      </c>
+      <c r="B112" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="C112" s="17" t="s">
+        <v>207</v>
+      </c>
+      <c r="D112" s="18" t="s">
+        <v>208</v>
+      </c>
+      <c r="E112" s="18" t="s">
+        <v>190</v>
+      </c>
+      <c r="F112" s="19" t="s">
+        <v>209</v>
+      </c>
+      <c r="G112" s="19" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A113" s="14" t="s">
+        <v>206</v>
+      </c>
+      <c r="B113" s="16" t="s">
+        <v>193</v>
+      </c>
+      <c r="C113" s="18" t="s">
+        <v>210</v>
+      </c>
+      <c r="D113" s="17" t="s">
+        <v>211</v>
+      </c>
+      <c r="E113" s="17" t="s">
+        <v>196</v>
+      </c>
+      <c r="F113" s="19" t="s">
+        <v>212</v>
+      </c>
+      <c r="G113" s="19" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A114" s="14" t="s">
+        <v>213</v>
+      </c>
+      <c r="B114" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="C114" s="17" t="s">
+        <v>214</v>
+      </c>
+      <c r="D114" s="18" t="s">
+        <v>215</v>
+      </c>
+      <c r="E114" s="18" t="s">
+        <v>190</v>
+      </c>
+      <c r="F114" s="19" t="s">
+        <v>216</v>
+      </c>
+      <c r="G114" s="19" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A115" s="14" t="s">
+        <v>213</v>
+      </c>
+      <c r="B115" s="16" t="s">
+        <v>193</v>
+      </c>
+      <c r="C115" s="18" t="s">
+        <v>217</v>
+      </c>
+      <c r="D115" s="17" t="s">
+        <v>218</v>
+      </c>
+      <c r="E115" s="17" t="s">
+        <v>196</v>
+      </c>
+      <c r="F115" s="19" t="s">
+        <v>219</v>
+      </c>
+      <c r="G115" s="19" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A116" s="14" t="s">
+        <v>220</v>
+      </c>
+      <c r="B116" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="C116" s="17" t="s">
+        <v>198</v>
+      </c>
+      <c r="D116" s="18" t="s">
+        <v>189</v>
+      </c>
+      <c r="E116" s="18" t="s">
+        <v>190</v>
+      </c>
+      <c r="F116" s="19" t="s">
+        <v>221</v>
+      </c>
+      <c r="G116" s="19" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A117" s="14" t="s">
+        <v>220</v>
+      </c>
+      <c r="B117" s="16" t="s">
+        <v>193</v>
+      </c>
+      <c r="C117" s="18" t="s">
+        <v>192</v>
+      </c>
+      <c r="D117" s="17" t="s">
+        <v>195</v>
+      </c>
+      <c r="E117" s="17" t="s">
+        <v>196</v>
+      </c>
+      <c r="F117" s="19" t="s">
+        <v>222</v>
+      </c>
+      <c r="G117" s="19" t="s">
+        <v>198</v>
       </c>
     </row>
   </sheetData>
